--- a/artfynd/A 44722-2025 artfynd.xlsx
+++ b/artfynd/A 44722-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>74463577</v>
       </c>
       <c r="B2" t="n">
-        <v>101692</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104061</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -711,10 +706,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>523576.6810612765</v>
+        <v>523577</v>
       </c>
       <c r="R2" t="n">
-        <v>6393317.996211261</v>
+        <v>6393318</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -744,19 +739,9 @@
           <t>1990-01-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1990-12-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">

--- a/artfynd/A 44722-2025 artfynd.xlsx
+++ b/artfynd/A 44722-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74463577</v>
       </c>
       <c r="B2" t="n">
-        <v>104061</v>
+        <v>104070</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 44722-2025 artfynd.xlsx
+++ b/artfynd/A 44722-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74463577</v>
       </c>
       <c r="B2" t="n">
-        <v>104070</v>
+        <v>104073</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 44722-2025 artfynd.xlsx
+++ b/artfynd/A 44722-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74463577</v>
       </c>
       <c r="B2" t="n">
-        <v>104073</v>
+        <v>104100</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 44722-2025 artfynd.xlsx
+++ b/artfynd/A 44722-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74463577</v>
       </c>
       <c r="B2" t="n">
-        <v>104100</v>
+        <v>104106</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 44722-2025 artfynd.xlsx
+++ b/artfynd/A 44722-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74463577</v>
       </c>
       <c r="B2" t="n">
-        <v>104106</v>
+        <v>104113</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 44722-2025 artfynd.xlsx
+++ b/artfynd/A 44722-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74463577</v>
       </c>
       <c r="B2" t="n">
-        <v>104113</v>
+        <v>104117</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 44722-2025 artfynd.xlsx
+++ b/artfynd/A 44722-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74463577</v>
       </c>
       <c r="B2" t="n">
-        <v>104117</v>
+        <v>104124</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 44722-2025 artfynd.xlsx
+++ b/artfynd/A 44722-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74463577</v>
       </c>
       <c r="B2" t="n">
-        <v>104127</v>
+        <v>104132</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 44722-2025 artfynd.xlsx
+++ b/artfynd/A 44722-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74463577</v>
       </c>
       <c r="B2" t="n">
-        <v>104132</v>
+        <v>104140</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 44722-2025 artfynd.xlsx
+++ b/artfynd/A 44722-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74463577</v>
       </c>
       <c r="B2" t="n">
-        <v>104140</v>
+        <v>104150</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
